--- a/data/trans_orig/P74A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P74A-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11500</t>
+          <t>12627</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6629</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2803</t>
+          <t>2713</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14420</t>
+          <t>15038</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>907</t>
+          <t>906</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7964</t>
+          <t>8726</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6979</t>
+          <t>7588</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2779</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12194</t>
+          <t>12737</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5111</t>
+          <t>6013</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5468</t>
+          <t>5110</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>251987</t>
+          <t>255766</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>294384</t>
+          <t>296145</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>56,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5408</t>
+          <t>5920</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>249012</t>
+          <t>247828</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>301665</t>
+          <t>304935</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>34,01%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17142</t>
+          <t>17407</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>36104</t>
+          <t>36086</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>111007</t>
+          <t>111785</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>147555</t>
+          <t>147899</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>132286</t>
+          <t>132026</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>177078</t>
+          <t>175556</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,58%</t>
         </is>
       </c>
     </row>
@@ -1410,12 +1410,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11855</t>
+          <t>11857</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29860</t>
+          <t>29394</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1445,12 +1445,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8983</t>
+          <t>8732</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23517</t>
+          <t>23930</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1460,12 +1460,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24476</t>
+          <t>23570</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46841</t>
+          <t>46362</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1495,12 +1495,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -1523,12 +1523,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>110794</t>
+          <t>109743</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>150051</t>
+          <t>147533</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1538,12 +1538,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1558,12 +1558,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>271656</t>
+          <t>271392</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>309660</t>
+          <t>309507</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1573,12 +1573,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>70,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1593,12 +1593,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>390385</t>
+          <t>390044</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>451389</t>
+          <t>449035</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1608,12 +1608,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>50,08%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>923</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9278</t>
+          <t>6624</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,47 +1768,47 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>3057</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>8376</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
           <t>0,15%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3057</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>992</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>9068</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2787</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12646</t>
+          <t>11946</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4395</t>
+          <t>4397</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3221</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15344</t>
+          <t>14297</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3857</t>
+          <t>3352</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15936</t>
+          <t>15807</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1979,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13192</t>
+          <t>12583</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1116</t>
+          <t>1109</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>13019</t>
+          <t>14667</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -2092,12 +2092,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>353385</t>
+          <t>351462</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>403656</t>
+          <t>404042</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2162,12 +2162,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>345354</t>
+          <t>345157</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>412395</t>
+          <t>410445</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2177,12 +2177,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,07%</t>
         </is>
       </c>
     </row>
@@ -2205,12 +2205,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19976</t>
+          <t>20149</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42522</t>
+          <t>40882</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2240,12 +2240,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>119044</t>
+          <t>120070</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>161850</t>
+          <t>163329</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2255,12 +2255,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2275,12 +2275,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>146152</t>
+          <t>144411</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>196896</t>
+          <t>193697</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2290,12 +2290,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,14%</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10003</t>
+          <t>9115</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6984</t>
+          <t>5330</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10157</t>
+          <t>9301</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -2431,12 +2431,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12381</t>
+          <t>11827</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30074</t>
+          <t>30740</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2446,12 +2446,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2466,12 +2466,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9706</t>
+          <t>8895</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26008</t>
+          <t>26080</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24475</t>
+          <t>24542</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>50361</t>
+          <t>50576</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -2544,12 +2544,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>176705</t>
+          <t>179017</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>226438</t>
+          <t>226636</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2579,12 +2579,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>451037</t>
+          <t>448105</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>496529</t>
+          <t>494357</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>69,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2614,12 +2614,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>637904</t>
+          <t>638353</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>710952</t>
+          <t>710337</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>55,51%</t>
         </is>
       </c>
     </row>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3752</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3717</t>
+          <t>3709</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5498</t>
+          <t>5485</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2922,12 +2922,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1733</t>
+          <t>1777</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9558</t>
+          <t>10277</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2957,12 +2957,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2689</t>
+          <t>2528</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>12395</t>
+          <t>12022</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9411</t>
+          <t>10065</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11046</t>
+          <t>10136</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -3113,12 +3113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>250816</t>
+          <t>254758</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>295349</t>
+          <t>297051</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4611</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>249035</t>
+          <t>246605</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>303887</t>
+          <t>302054</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3198,12 +3198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,29%</t>
         </is>
       </c>
     </row>
@@ -3226,12 +3226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11903</t>
+          <t>12082</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>31071</t>
+          <t>29637</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3241,12 +3241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>86257</t>
+          <t>85083</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>120755</t>
+          <t>119261</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3276,12 +3276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>99550</t>
+          <t>100239</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>142691</t>
+          <t>142512</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,71%</t>
         </is>
       </c>
     </row>
@@ -3452,12 +3452,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>13139</t>
+          <t>13011</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>31826</t>
+          <t>31772</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3487,12 +3487,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7872</t>
+          <t>7891</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>22614</t>
+          <t>21945</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3502,12 +3502,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3522,12 +3522,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>24426</t>
+          <t>23372</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>48093</t>
+          <t>46731</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -3565,12 +3565,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>130992</t>
+          <t>128934</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>174781</t>
+          <t>170992</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3580,12 +3580,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3600,12 +3600,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>296203</t>
+          <t>296085</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>332012</t>
+          <t>332558</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3615,12 +3615,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,74%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3635,12 +3635,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>437196</t>
+          <t>438072</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>497739</t>
+          <t>501647</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>55,28%</t>
         </is>
       </c>
     </row>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6088</t>
+          <t>6288</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3830,12 +3830,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2173</t>
+          <t>2232</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>13539</t>
+          <t>13566</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3865,12 +3865,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3382</t>
+          <t>3087</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>15420</t>
+          <t>15829</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -3908,12 +3908,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>837</t>
+          <t>836</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>9441</t>
+          <t>9630</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3943,12 +3943,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1928</t>
+          <t>1937</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>10711</t>
+          <t>11500</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3978,12 +3978,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3839</t>
+          <t>3855</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>15736</t>
+          <t>16653</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,7 +3998,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -4021,12 +4021,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>3286</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>15442</t>
+          <t>15799</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4036,12 +4036,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>3373</t>
+          <t>3283</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>15705</t>
+          <t>15316</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -4134,12 +4134,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>272236</t>
+          <t>271876</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>318510</t>
+          <t>319509</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4149,12 +4149,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>10161</t>
+          <t>10853</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>270199</t>
+          <t>269488</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>326254</t>
+          <t>327798</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,06%</t>
         </is>
       </c>
     </row>
@@ -4247,12 +4247,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>11806</t>
+          <t>11527</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>30207</t>
+          <t>29317</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4262,12 +4262,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4282,12 +4282,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>127610</t>
+          <t>127191</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>167423</t>
+          <t>169388</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>143089</t>
+          <t>145030</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>190235</t>
+          <t>192928</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,52%</t>
         </is>
       </c>
     </row>
@@ -4473,12 +4473,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>14278</t>
+          <t>14825</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>32850</t>
+          <t>32374</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4488,12 +4488,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4508,12 +4508,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>11810</t>
+          <t>10932</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>29701</t>
+          <t>29203</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>29724</t>
+          <t>29537</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>55281</t>
+          <t>54046</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -4586,12 +4586,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>205317</t>
+          <t>204304</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>251247</t>
+          <t>251635</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4601,12 +4601,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>43,73%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>389708</t>
+          <t>390857</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>434213</t>
+          <t>434132</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4656,12 +4656,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>610003</t>
+          <t>611183</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>675703</t>
+          <t>675446</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>52,33%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>57,83%</t>
         </is>
       </c>
     </row>
@@ -4816,12 +4816,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>4509</t>
+          <t>4658</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>17646</t>
+          <t>17723</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4831,12 +4831,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4851,12 +4851,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>6286</t>
+          <t>6038</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>20973</t>
+          <t>20466</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4866,12 +4866,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4886,12 +4886,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>12696</t>
+          <t>13177</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>33030</t>
+          <t>32970</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -4929,12 +4929,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>4294</t>
+          <t>4411</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>15994</t>
+          <t>16658</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4944,12 +4944,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>12616</t>
+          <t>12961</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>29959</t>
+          <t>31212</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4979,12 +4979,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4999,12 +4999,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>19615</t>
+          <t>20135</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>40989</t>
+          <t>41556</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -5042,12 +5042,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>8866</t>
+          <t>8714</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>29207</t>
+          <t>27401</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5112,12 +5112,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>8865</t>
+          <t>8464</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>27600</t>
+          <t>27734</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1173978</t>
+          <t>1175937</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1267977</t>
+          <t>1269272</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>1799</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>12333</t>
+          <t>13001</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5225,12 +5225,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1165854</t>
+          <t>1161259</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1288817</t>
+          <t>1287452</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,28%</t>
         </is>
       </c>
     </row>
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>76496</t>
+          <t>75443</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>112681</t>
+          <t>112186</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5303,12 +5303,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>477575</t>
+          <t>476672</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>553038</t>
+          <t>553390</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5338,12 +5338,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>561459</t>
+          <t>565015</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>653263</t>
+          <t>654711</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,4%</t>
         </is>
       </c>
     </row>
@@ -5386,7 +5386,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>10276</t>
+          <t>9147</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>5838</t>
+          <t>5548</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>9094</t>
+          <t>11088</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,26%</t>
         </is>
       </c>
     </row>
@@ -5494,12 +5494,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>66440</t>
+          <t>64618</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>101891</t>
+          <t>99839</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5509,12 +5509,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5529,12 +5529,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>48793</t>
+          <t>49175</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>80321</t>
+          <t>80018</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>123011</t>
+          <t>122776</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>169233</t>
+          <t>170559</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -5607,12 +5607,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>661222</t>
+          <t>661073</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>751568</t>
+          <t>752638</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5642,12 +5642,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>1454674</t>
+          <t>1452531</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>1536015</t>
+          <t>1536680</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5657,12 +5657,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5677,12 +5677,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>2140430</t>
+          <t>2132983</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>2271614</t>
+          <t>2266931</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>53,32%</t>
         </is>
       </c>
     </row>
@@ -6109,7 +6109,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10704</t>
+          <t>9246</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9808</t>
+          <t>12244</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6159,7 +6159,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11988</t>
+          <t>11173</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6217,12 +6217,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4373</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18692</t>
+          <t>18470</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6232,12 +6232,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6252,12 +6252,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6364</t>
+          <t>6827</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22551</t>
+          <t>22717</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6267,12 +6267,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5346</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6315,7 +6315,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9489</t>
+          <t>10460</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6370,7 +6370,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11245</t>
+          <t>10233</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -6408,12 +6408,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>184828</t>
+          <t>182115</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>227173</t>
+          <t>225643</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6423,12 +6423,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>49,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6448,7 +6448,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5215</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6478,12 +6478,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>180371</t>
+          <t>181406</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>233296</t>
+          <t>233081</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,51%</t>
         </is>
       </c>
     </row>
@@ -6521,12 +6521,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27419</t>
+          <t>28230</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>52892</t>
+          <t>53043</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6536,12 +6536,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6556,12 +6556,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>87293</t>
+          <t>88808</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>122487</t>
+          <t>124823</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6571,12 +6571,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6591,12 +6591,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>122269</t>
+          <t>122295</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>166362</t>
+          <t>166155</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,18%</t>
         </is>
       </c>
     </row>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4358</t>
+          <t>5829</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5213</t>
+          <t>5719</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -6747,12 +6747,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48372</t>
+          <t>48227</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>78041</t>
+          <t>75361</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6762,12 +6762,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6782,12 +6782,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>63993</t>
+          <t>62310</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>96813</t>
+          <t>96503</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>120579</t>
+          <t>117579</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>164370</t>
+          <t>162285</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,76%</t>
         </is>
       </c>
     </row>
@@ -6860,12 +6860,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>123079</t>
+          <t>125672</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>165576</t>
+          <t>165521</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6875,12 +6875,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6895,12 +6895,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>240338</t>
+          <t>241645</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>281748</t>
+          <t>285769</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>371155</t>
+          <t>377026</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>434536</t>
+          <t>442213</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>48,39%</t>
         </is>
       </c>
     </row>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12758</t>
+          <t>13346</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7165,7 +7165,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12520</t>
+          <t>14079</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -7203,12 +7203,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10141</t>
+          <t>11000</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7223,7 +7223,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7238,12 +7238,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11790</t>
+          <t>11745</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30860</t>
+          <t>29609</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14983</t>
+          <t>14854</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>36793</t>
+          <t>37332</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -7316,12 +7316,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>980</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9857</t>
+          <t>8824</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10707</t>
+          <t>11069</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2864</t>
+          <t>2928</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>14767</t>
+          <t>14970</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -7429,12 +7429,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>248754</t>
+          <t>251421</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>301714</t>
+          <t>301876</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5516</t>
+          <t>5506</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7499,12 +7499,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>248706</t>
+          <t>248984</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>307879</t>
+          <t>308401</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,83%</t>
         </is>
       </c>
     </row>
@@ -7542,12 +7542,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25202</t>
+          <t>26685</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>52584</t>
+          <t>53131</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>129847</t>
+          <t>128949</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>173869</t>
+          <t>175937</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>162335</t>
+          <t>161515</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>214934</t>
+          <t>214307</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,86%</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7012</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7675,7 +7675,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7695,7 +7695,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5992</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7710,7 +7710,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7964</t>
+          <t>8772</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7745,7 +7745,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -7768,12 +7768,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>85443</t>
+          <t>86401</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>125053</t>
+          <t>123377</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>90866</t>
+          <t>90838</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>131124</t>
+          <t>130331</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7818,12 +7818,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7838,12 +7838,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>183746</t>
+          <t>185634</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>239232</t>
+          <t>241616</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7853,12 +7853,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,89%</t>
         </is>
       </c>
     </row>
@@ -7881,12 +7881,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>212631</t>
+          <t>212069</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265480</t>
+          <t>264045</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>372432</t>
+          <t>373679</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>423767</t>
+          <t>428848</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7931,12 +7931,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>54,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7951,12 +7951,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>600776</t>
+          <t>601310</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>679389</t>
+          <t>675529</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7966,12 +7966,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>50,01%</t>
         </is>
       </c>
     </row>
@@ -8151,7 +8151,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8229</t>
+          <t>7418</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7183</t>
+          <t>6383</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -8229,7 +8229,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7489</t>
+          <t>6558</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>8332</t>
+          <t>8230</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>25420</t>
+          <t>26869</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8274,12 +8274,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8294,12 +8294,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>9276</t>
+          <t>10117</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>28742</t>
+          <t>29039</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8309,12 +8309,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -8337,12 +8337,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2220</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17017</t>
+          <t>16394</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8377,7 +8377,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6894</t>
+          <t>7031</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8407,12 +8407,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3097</t>
+          <t>4046</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>18834</t>
+          <t>18396</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8422,12 +8422,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -8450,12 +8450,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>194990</t>
+          <t>196004</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>243117</t>
+          <t>244103</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8465,12 +8465,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8520,12 +8520,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>191345</t>
+          <t>192205</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>245049</t>
+          <t>247954</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8535,12 +8535,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,49%</t>
         </is>
       </c>
     </row>
@@ -8563,12 +8563,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>12701</t>
+          <t>12151</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>32618</t>
+          <t>31685</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8578,12 +8578,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8598,12 +8598,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>88264</t>
+          <t>85244</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>126307</t>
+          <t>124058</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8613,12 +8613,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8633,12 +8633,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>105717</t>
+          <t>102173</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>149279</t>
+          <t>149168</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8648,12 +8648,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,73%</t>
         </is>
       </c>
     </row>
@@ -8681,7 +8681,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>7338</t>
+          <t>5849</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -8696,7 +8696,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>7159</t>
+          <t>6341</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>939</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>8293</t>
+          <t>8301</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -8789,12 +8789,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>39181</t>
+          <t>39313</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>69014</t>
+          <t>70745</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8804,12 +8804,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>55003</t>
+          <t>55543</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>86435</t>
+          <t>87483</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8839,12 +8839,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>102235</t>
+          <t>100630</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>143255</t>
+          <t>145180</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8874,12 +8874,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,34%</t>
         </is>
       </c>
     </row>
@@ -8902,12 +8902,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>173140</t>
+          <t>171522</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>220218</t>
+          <t>218656</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8917,12 +8917,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>294952</t>
+          <t>290591</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>341003</t>
+          <t>340793</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8952,12 +8952,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>481580</t>
+          <t>482951</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>547469</t>
+          <t>550075</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8987,12 +8987,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>54,33%</t>
         </is>
       </c>
     </row>
@@ -9137,7 +9137,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>10576</t>
+          <t>10241</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -9152,7 +9152,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -9207,7 +9207,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>11242</t>
+          <t>11312</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -9245,12 +9245,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2977</t>
+          <t>2930</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>13130</t>
+          <t>13781</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -9260,12 +9260,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9280,12 +9280,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>7568</t>
+          <t>7230</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>24117</t>
+          <t>24386</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -9295,12 +9295,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -9315,12 +9315,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>12642</t>
+          <t>13565</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>31763</t>
+          <t>34777</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9330,12 +9330,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -9358,12 +9358,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>5029</t>
+          <t>4921</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>17682</t>
+          <t>18515</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -9373,12 +9373,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -9393,12 +9393,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>939</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>7755</t>
+          <t>8569</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -9413,7 +9413,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>7045</t>
+          <t>6798</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>22227</t>
+          <t>21093</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -9443,12 +9443,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -9471,12 +9471,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>240061</t>
+          <t>239369</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>290377</t>
+          <t>291315</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9486,12 +9486,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>10593</t>
+          <t>11441</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>237470</t>
+          <t>237857</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>294528</t>
+          <t>297043</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,2%</t>
         </is>
       </c>
     </row>
@@ -9584,12 +9584,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>18963</t>
+          <t>18373</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>42091</t>
+          <t>42963</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9599,12 +9599,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>157319</t>
+          <t>157407</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>204852</t>
+          <t>202229</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>182218</t>
+          <t>181841</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>235371</t>
+          <t>238385</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9669,12 +9669,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,42%</t>
         </is>
       </c>
     </row>
@@ -9702,7 +9702,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6570</t>
+          <t>6112</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9717,7 +9717,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9737,7 +9737,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5504</t>
+          <t>5708</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9752,7 +9752,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9767,12 +9767,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>937</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>8964</t>
+          <t>8343</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9787,7 +9787,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -9810,12 +9810,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>47778</t>
+          <t>47255</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>78507</t>
+          <t>78013</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9845,12 +9845,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>45102</t>
+          <t>47463</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>75151</t>
+          <t>77563</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9860,12 +9860,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9880,12 +9880,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>103019</t>
+          <t>100713</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>144177</t>
+          <t>143523</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9895,12 +9895,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -9923,12 +9923,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>192554</t>
+          <t>190446</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>239978</t>
+          <t>240586</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9938,12 +9938,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9958,12 +9958,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>349825</t>
+          <t>350259</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>400941</t>
+          <t>399325</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9973,12 +9973,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>62,87%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9993,12 +9993,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>557161</t>
+          <t>557979</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>630142</t>
+          <t>629283</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -10008,12 +10008,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,27%</t>
         </is>
       </c>
     </row>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>1863</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>15953</t>
+          <t>17230</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -10168,82 +10168,82 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>3932</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>11294</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>0,04%</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>10256</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>4094</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>21119</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
           <t>0,09%</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>3932</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>996</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>11827</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>0,04%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>10256</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>4623</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>22291</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -10266,12 +10266,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>9852</t>
+          <t>9521</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>27975</t>
+          <t>27017</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -10281,12 +10281,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -10301,12 +10301,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>43438</t>
+          <t>42366</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>78345</t>
+          <t>75814</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -10316,12 +10316,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>57827</t>
+          <t>57658</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>93690</t>
+          <t>97065</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10356,7 +10356,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -10379,12 +10379,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>13724</t>
+          <t>13389</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>34898</t>
+          <t>33926</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10394,12 +10394,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10414,12 +10414,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>4777</t>
+          <t>4798</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>19237</t>
+          <t>19455</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>21701</t>
+          <t>20708</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>45942</t>
+          <t>44864</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10464,12 +10464,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -10492,12 +10492,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>914469</t>
+          <t>919230</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1013327</t>
+          <t>1013438</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10507,12 +10507,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10527,12 +10527,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>13158</t>
+          <t>10907</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10547,7 +10547,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>908417</t>
+          <t>914969</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1022247</t>
+          <t>1026551</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10577,12 +10577,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,79%</t>
         </is>
       </c>
     </row>
@@ -10605,12 +10605,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>103175</t>
+          <t>103341</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>148289</t>
+          <t>151349</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10620,12 +10620,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10640,12 +10640,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>495959</t>
+          <t>499637</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>581203</t>
+          <t>584440</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10655,12 +10655,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10675,12 +10675,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>615244</t>
+          <t>618438</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>712553</t>
+          <t>713426</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10690,12 +10690,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,84%</t>
         </is>
       </c>
     </row>
@@ -10718,12 +10718,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>2862</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>13639</t>
+          <t>13525</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -10753,12 +10753,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>994</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>8851</t>
+          <t>10154</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -10773,7 +10773,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -10788,12 +10788,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>5025</t>
+          <t>5255</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>17908</t>
+          <t>19041</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -10803,12 +10803,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,42%</t>
         </is>
       </c>
     </row>
@@ -10831,12 +10831,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>248286</t>
+          <t>245461</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>313673</t>
+          <t>312745</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -10846,12 +10846,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -10866,12 +10866,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>285507</t>
+          <t>285858</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>350339</t>
+          <t>356654</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -10881,12 +10881,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -10901,12 +10901,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>557010</t>
+          <t>545548</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>646098</t>
+          <t>641578</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -10916,12 +10916,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,24%</t>
         </is>
       </c>
     </row>
@@ -10944,12 +10944,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>745046</t>
+          <t>745973</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>838022</t>
+          <t>838094</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -10959,7 +10959,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>1301316</t>
+          <t>1305083</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>1402010</t>
+          <t>1406276</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -10994,12 +10994,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>56,95%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>61,18%</t>
+          <t>61,37%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -11014,12 +11014,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>2078607</t>
+          <t>2071057</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>2211212</t>
+          <t>2216588</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -11029,12 +11029,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>49,21%</t>
         </is>
       </c>
     </row>
@@ -11411,7 +11411,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7344</t>
+          <t>6712</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11426,7 +11426,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11446,7 +11446,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>3907</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11461,7 +11461,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>911</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8070</t>
+          <t>8846</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11496,7 +11496,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8571</t>
+          <t>7590</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11554,12 +11554,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>1719</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10591</t>
+          <t>9894</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11569,12 +11569,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11589,12 +11589,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2799</t>
+          <t>2879</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13081</t>
+          <t>14119</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6366</t>
+          <t>6046</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11707,7 +11707,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>6143</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11722,7 +11722,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -11745,12 +11745,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>164619</t>
+          <t>167205</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>208605</t>
+          <t>208587</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11760,7 +11760,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6055</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11800,7 +11800,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11815,12 +11815,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>165906</t>
+          <t>165986</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>215906</t>
+          <t>213030</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11830,12 +11830,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,82%</t>
         </is>
       </c>
     </row>
@@ -11858,12 +11858,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17555</t>
+          <t>16921</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>36703</t>
+          <t>35731</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11873,12 +11873,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11893,12 +11893,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>112603</t>
+          <t>107984</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>149209</t>
+          <t>148126</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11908,12 +11908,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11928,12 +11928,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>134009</t>
+          <t>135414</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>182851</t>
+          <t>178783</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11943,12 +11943,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>20,83%</t>
         </is>
       </c>
     </row>
@@ -12011,7 +12011,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4957</t>
+          <t>4947</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -12026,7 +12026,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -12046,7 +12046,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -12061,7 +12061,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -12084,12 +12084,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>72324</t>
+          <t>71458</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>106191</t>
+          <t>104823</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12099,12 +12099,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12119,12 +12119,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>58075</t>
+          <t>57691</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>89241</t>
+          <t>88780</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12134,12 +12134,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12154,12 +12154,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>139352</t>
+          <t>137740</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>185760</t>
+          <t>182963</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12169,12 +12169,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,32%</t>
         </is>
       </c>
     </row>
@@ -12197,12 +12197,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>105047</t>
+          <t>105010</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>141847</t>
+          <t>140665</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12212,12 +12212,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12232,12 +12232,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>198669</t>
+          <t>199217</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>238648</t>
+          <t>239659</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12247,12 +12247,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12267,12 +12267,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>315208</t>
+          <t>313827</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>372178</t>
+          <t>370439</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12282,12 +12282,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>43,17%</t>
         </is>
       </c>
     </row>
@@ -12432,7 +12432,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4844</t>
+          <t>4131</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12447,7 +12447,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12462,12 +12462,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>896</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8547</t>
+          <t>8517</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12482,7 +12482,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12497,12 +12497,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>986</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10339</t>
+          <t>9520</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12512,12 +12512,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -12540,12 +12540,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3650</t>
+          <t>3843</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18581</t>
+          <t>19381</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12555,12 +12555,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12575,12 +12575,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4090</t>
+          <t>4105</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16992</t>
+          <t>17996</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12595,7 +12595,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12610,12 +12610,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10315</t>
+          <t>10112</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>30384</t>
+          <t>29352</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12625,12 +12625,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -12653,12 +12653,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12474</t>
+          <t>12162</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12668,12 +12668,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -12693,7 +12693,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8381</t>
+          <t>9158</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12708,7 +12708,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -12723,12 +12723,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2874</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>14610</t>
+          <t>15022</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12743,7 +12743,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -12766,12 +12766,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>259468</t>
+          <t>260250</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>311277</t>
+          <t>309935</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12781,12 +12781,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12806,7 +12806,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5819</t>
+          <t>6349</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12821,7 +12821,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12836,12 +12836,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>257297</t>
+          <t>256741</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>318830</t>
+          <t>320025</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12851,12 +12851,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,03%</t>
         </is>
       </c>
     </row>
@@ -12879,12 +12879,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12808</t>
+          <t>13082</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31906</t>
+          <t>31548</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12894,12 +12894,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12914,12 +12914,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>147529</t>
+          <t>149614</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>198130</t>
+          <t>196933</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12929,12 +12929,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12949,12 +12949,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>169056</t>
+          <t>168657</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>222499</t>
+          <t>226435</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12964,12 +12964,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>17,0%</t>
         </is>
       </c>
     </row>
@@ -12997,7 +12997,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5573</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13012,7 +13012,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5395</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13047,7 +13047,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13067,7 +13067,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8362</t>
+          <t>6317</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13082,7 +13082,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -13105,12 +13105,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>87162</t>
+          <t>87989</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>127670</t>
+          <t>125767</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13120,12 +13120,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13140,12 +13140,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>83782</t>
+          <t>82619</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>121471</t>
+          <t>121625</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13155,12 +13155,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13175,12 +13175,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>183014</t>
+          <t>183213</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>236365</t>
+          <t>238880</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13190,12 +13190,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,93%</t>
         </is>
       </c>
     </row>
@@ -13218,12 +13218,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>187195</t>
+          <t>186774</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>236119</t>
+          <t>237316</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13233,12 +13233,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13253,12 +13253,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>372245</t>
+          <t>371882</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>426112</t>
+          <t>424138</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13268,12 +13268,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13288,12 +13288,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>572462</t>
+          <t>573985</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>648094</t>
+          <t>649709</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13303,12 +13303,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,78%</t>
         </is>
       </c>
     </row>
@@ -13483,47 +13483,47 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t>938</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>8417</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>3040</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
           <t>935</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>7511</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>3040</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>938</t>
-        </is>
-      </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9032</t>
+          <t>8244</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13538,7 +13538,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -13566,7 +13566,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7329</t>
+          <t>7309</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13596,12 +13596,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1031</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10180</t>
+          <t>10156</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13616,7 +13616,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13631,12 +13631,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3009</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>14002</t>
+          <t>12275</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13646,12 +13646,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -13674,12 +13674,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9170</t>
+          <t>8230</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13694,7 +13694,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13714,7 +13714,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6600</t>
+          <t>6101</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13729,7 +13729,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13744,12 +13744,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10969</t>
+          <t>10977</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>227483</t>
+          <t>229459</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>273162</t>
+          <t>274556</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13802,12 +13802,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13827,7 +13827,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6268</t>
+          <t>5009</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13842,7 +13842,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13857,12 +13857,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>224359</t>
+          <t>224601</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>280428</t>
+          <t>281254</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13872,12 +13872,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,37%</t>
         </is>
       </c>
     </row>
@@ -13900,12 +13900,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6942</t>
+          <t>6827</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>21407</t>
+          <t>21976</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13915,12 +13915,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13935,12 +13935,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>98153</t>
+          <t>97491</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>136399</t>
+          <t>138153</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13950,12 +13950,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13970,12 +13970,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>107558</t>
+          <t>107302</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>149643</t>
+          <t>153397</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13985,12 +13985,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>16,02%</t>
         </is>
       </c>
     </row>
@@ -14053,7 +14053,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>6090</t>
+          <t>6032</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -14068,7 +14068,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -14088,7 +14088,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7024</t>
+          <t>6965</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -14126,12 +14126,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>57251</t>
+          <t>55137</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>87760</t>
+          <t>88461</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14141,12 +14141,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14161,12 +14161,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>56301</t>
+          <t>55897</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>86427</t>
+          <t>85806</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14176,12 +14176,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14196,12 +14196,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>119379</t>
+          <t>118585</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>162120</t>
+          <t>164235</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14211,12 +14211,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,15%</t>
         </is>
       </c>
     </row>
@@ -14239,12 +14239,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>122883</t>
+          <t>124564</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>167566</t>
+          <t>165220</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14254,12 +14254,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14274,12 +14274,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>255058</t>
+          <t>251602</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>296343</t>
+          <t>296796</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14289,12 +14289,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14309,12 +14309,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>388279</t>
+          <t>389427</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>452143</t>
+          <t>449177</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14324,12 +14324,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>46,91%</t>
         </is>
       </c>
     </row>
@@ -14474,7 +14474,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>8804</t>
+          <t>8221</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14489,7 +14489,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14509,7 +14509,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6833</t>
+          <t>7122</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14524,7 +14524,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14539,12 +14539,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1063</t>
+          <t>1161</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>10947</t>
+          <t>11921</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14554,12 +14554,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -14582,12 +14582,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1467</t>
+          <t>1582</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>12198</t>
+          <t>10941</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14597,12 +14597,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14617,12 +14617,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>11667</t>
+          <t>11498</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14637,7 +14637,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14652,12 +14652,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4854</t>
+          <t>4680</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>17140</t>
+          <t>17541</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14667,12 +14667,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -14695,12 +14695,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2967</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>13436</t>
+          <t>13409</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -14710,12 +14710,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -14735,7 +14735,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>6705</t>
+          <t>6734</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -14750,7 +14750,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -14765,12 +14765,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>3934</t>
+          <t>4542</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>15599</t>
+          <t>16105</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -14780,12 +14780,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -14808,12 +14808,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>228727</t>
+          <t>228970</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>278512</t>
+          <t>274109</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14823,12 +14823,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14878,12 +14878,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>227403</t>
+          <t>226340</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>281288</t>
+          <t>279899</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14893,12 +14893,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,57%</t>
         </is>
       </c>
     </row>
@@ -14921,12 +14921,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>24560</t>
+          <t>24331</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>45502</t>
+          <t>46860</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14936,12 +14936,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14956,12 +14956,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>128795</t>
+          <t>127212</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>173081</t>
+          <t>172642</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14971,12 +14971,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14991,12 +14991,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>156594</t>
+          <t>160150</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>208061</t>
+          <t>211544</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -15006,12 +15006,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,57%</t>
         </is>
       </c>
     </row>
@@ -15039,7 +15039,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5446</t>
+          <t>5393</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -15054,7 +15054,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -15109,7 +15109,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6218</t>
+          <t>5819</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -15124,7 +15124,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -15147,12 +15147,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>57245</t>
+          <t>58527</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>90825</t>
+          <t>90084</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -15182,12 +15182,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>50784</t>
+          <t>50261</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>80220</t>
+          <t>82010</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -15197,12 +15197,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -15217,12 +15217,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>115964</t>
+          <t>116087</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>159888</t>
+          <t>160384</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -15232,12 +15232,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,08%</t>
         </is>
       </c>
     </row>
@@ -15260,12 +15260,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>195020</t>
+          <t>197569</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>244706</t>
+          <t>243565</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -15275,12 +15275,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -15295,12 +15295,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>296702</t>
+          <t>296280</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>343976</t>
+          <t>345369</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -15310,12 +15310,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -15330,12 +15330,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>507252</t>
+          <t>509331</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>575227</t>
+          <t>572884</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -15345,12 +15345,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>50,3%</t>
         </is>
       </c>
     </row>
@@ -15490,12 +15490,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>12049</t>
+          <t>12937</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -15505,82 +15505,82 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>9241</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>4424</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>17072</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>14603</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>7954</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>24059</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
           <t>0,56%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>9241</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>4574</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>16973</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>14603</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>8689</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>25327</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="W40" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -15603,12 +15603,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>10745</t>
+          <t>10187</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>29311</t>
+          <t>29409</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -15618,12 +15618,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -15638,12 +15638,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>14418</t>
+          <t>14221</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>33654</t>
+          <t>33220</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15658,7 +15658,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15673,12 +15673,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>28842</t>
+          <t>29903</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>56491</t>
+          <t>57336</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15688,12 +15688,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -15716,12 +15716,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>10262</t>
+          <t>10114</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>27405</t>
+          <t>26226</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15731,12 +15731,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15751,12 +15751,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1879</t>
+          <t>1897</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>11457</t>
+          <t>13546</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15771,7 +15771,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15786,12 +15786,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>15046</t>
+          <t>14126</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>33793</t>
+          <t>33528</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15801,12 +15801,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -15829,12 +15829,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>933571</t>
+          <t>927190</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1026449</t>
+          <t>1025121</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15844,12 +15844,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15864,12 +15864,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>999</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>8913</t>
+          <t>8940</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15899,12 +15899,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>926804</t>
+          <t>925638</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1040763</t>
+          <t>1036933</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15914,12 +15914,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,19%</t>
         </is>
       </c>
     </row>
@@ -15942,12 +15942,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>76106</t>
+          <t>76065</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>114126</t>
+          <t>113761</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15962,7 +15962,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15977,12 +15977,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>527776</t>
+          <t>528333</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>615495</t>
+          <t>613952</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15992,12 +15992,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -16012,12 +16012,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>607895</t>
+          <t>617887</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>711763</t>
+          <t>718816</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -16027,12 +16027,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,77%</t>
         </is>
       </c>
     </row>
@@ -16055,12 +16055,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>888</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>8401</t>
+          <t>7578</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -16075,7 +16075,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -16090,12 +16090,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>9989</t>
+          <t>10166</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -16110,7 +16110,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -16125,12 +16125,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>2863</t>
+          <t>2851</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>13551</t>
+          <t>13346</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -16145,7 +16145,7 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
     </row>
@@ -16168,12 +16168,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>303428</t>
+          <t>304969</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>373610</t>
+          <t>371612</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -16183,12 +16183,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -16203,12 +16203,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>275921</t>
+          <t>278405</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>339834</t>
+          <t>342273</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -16218,12 +16218,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -16238,12 +16238,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>602816</t>
+          <t>602436</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>700169</t>
+          <t>698297</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -16253,12 +16253,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,29%</t>
         </is>
       </c>
     </row>
@@ -16281,12 +16281,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>660239</t>
+          <t>656397</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>749881</t>
+          <t>744676</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -16296,12 +16296,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -16316,12 +16316,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>1164976</t>
+          <t>1167431</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>1257976</t>
+          <t>1263792</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -16331,12 +16331,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>54,65%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -16351,12 +16351,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1849329</t>
+          <t>1843050</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>1980481</t>
+          <t>1975625</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -16366,12 +16366,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>46,09%</t>
         </is>
       </c>
     </row>
